--- a/3k2s/Экономика IT-компании/Лабораторная_работа_3_Точка_без_с (1).xlsx
+++ b/3k2s/Экономика IT-компании/Лабораторная_работа_3_Точка_без_с (1).xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vugor\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\General\BELSTU\3k2s\Экономика IT-компании\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -119,9 +119,6 @@
     <t>Цена 1 шт (без НДС), руб.</t>
   </si>
   <si>
-    <t>Условно-переменные на 1ш т, руб. (Собщ-УПР)/В</t>
-  </si>
-  <si>
     <t>Точка окупаемости, шт</t>
   </si>
   <si>
@@ -177,22 +174,7 @@
     <t>17. Рентабельность продукции, %</t>
   </si>
   <si>
-    <t>1. МЗ, руб. (п2*п1+п3*п4*п1+п15)</t>
-  </si>
-  <si>
-    <t>2. ФОТ, руб. ((п5*п1)+п6))</t>
-  </si>
-  <si>
     <t>3. Отчисления в ФСЗН, руб. (34% от ФОТ)</t>
-  </si>
-  <si>
-    <t>4. Амортизационные отчисления, руб. (п7+п8)*п9/100</t>
-  </si>
-  <si>
-    <t>5. Прочие, руб. (п10+п11+п12+п13+п14+п16)</t>
-  </si>
-  <si>
-    <t>Условно-постоянные (УПР), тыс. руб. (п. 6*1,34+п.7*п.9/100+п.11+п.12+п.13+п.16)</t>
   </si>
   <si>
     <r>
@@ -557,6 +539,24 @@
   </si>
   <si>
     <t>Прибыль, тыс руб</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Условно-переменные на 1ш т, руб. </t>
+  </si>
+  <si>
+    <t>Условно-постоянные (УПР), тыс. руб.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Прочие, руб. </t>
+  </si>
+  <si>
+    <t>4. Амортизационные отчисления, руб.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. ФОТ, руб. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. МЗ, руб. </t>
   </si>
 </sst>
 </file>
@@ -970,7 +970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1112,6 +1112,21 @@
     <xf numFmtId="3" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1130,20 +1145,23 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="2" fontId="18" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="23" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1771,12 +1789,296 @@
               </a:sp3d>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000010-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001A-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000012-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000013-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000014-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000015-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000016-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000017-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.728597347780341E-2"/>
+                  <c:y val="2.8125325268279433E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001B-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000018-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000019-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Исх данные решение'!$E$67:$E$81</c:f>
+              <c:f>'Исх данные решение'!$E$67:$E$80</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>5086.833333333333</c:v>
                 </c:pt>
@@ -1784,13 +2086,13 @@
                   <c:v>7630.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>10173.666666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12717.083333333334</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>14142.1482635142</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10173.666666666666</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>12717.083333333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>15260.5</c:v>
@@ -1818,19 +2120,16 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>35607.833333333336</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>30521</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Исх данные решение'!$F$67:$F$81</c:f>
+              <c:f>'Исх данные решение'!$F$67:$F$80</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>8614.7333333333336</c:v>
                 </c:pt>
@@ -1838,13 +2137,13 @@
                   <c:v>11158.15</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>13701.566666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16244.983333333334</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>17670.0482635142</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>13701.566666666666</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>16244.983333333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>18788.400000000001</c:v>
@@ -1872,9 +2171,6 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>39135.733333333337</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>34048.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1968,12 +2264,365 @@
               </a:sp3d>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.0230982689550994E-2"/>
+                  <c:y val="0.1396120530036197"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:noAutofit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.27083977611109988"/>
+                      <c:h val="5.7253122760031923E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.29926700465093459"/>
+                  <c:y val="-0.1078247738869309"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:noAutofit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.25356911636773632"/>
+                      <c:h val="5.2565568548652013E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-033C-41C0-82FF-4DEA4BB4DC76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Исх данные решение'!$E$67:$E$81</c:f>
+              <c:f>'Исх данные решение'!$E$67:$E$80</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>5086.833333333333</c:v>
                 </c:pt>
@@ -1981,13 +2630,13 @@
                   <c:v>7630.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>10173.666666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12717.083333333334</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>14142.1482635142</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10173.666666666666</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>12717.083333333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>15260.5</c:v>
@@ -2015,19 +2664,16 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>35607.833333333336</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>30521</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Исх данные решение'!$G$67:$G$81</c:f>
+              <c:f>'Исх данные решение'!$G$67:$G$80</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>6355.7946666666667</c:v>
                 </c:pt>
@@ -2035,13 +2681,13 @@
                   <c:v>9533.6919999999991</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>12711.589333333333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15889.486666666668</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>17670.048263514203</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>12711.589333333333</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>15889.486666666668</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>19067.383999999998</c:v>
@@ -2069,9 +2715,6 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>44490.562666666672</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>38134.767999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4129,7 +4772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
@@ -4138,46 +4781,47 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="8.77734375" customWidth="1"/>
     <col min="6" max="6" width="8.21875" customWidth="1"/>
-    <col min="7" max="7" width="8.77734375" customWidth="1"/>
-    <col min="8" max="9" width="7.5546875" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" customWidth="1"/>
+    <col min="9" max="9" width="7.5546875" customWidth="1"/>
     <col min="10" max="10" width="8.44140625" customWidth="1"/>
     <col min="11" max="11" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="90.3" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="68" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
+      <c r="A1" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
     </row>
     <row r="2" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="67"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="72"/>
     </row>
     <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A3" s="64"/>
+      <c r="A3" s="69"/>
       <c r="B3" s="8">
         <v>1</v>
       </c>
@@ -4216,10 +4860,10 @@
       <c r="B4" s="10">
         <v>48000</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="65">
         <v>60000</v>
       </c>
-      <c r="D4" s="69">
+      <c r="D4" s="63">
         <v>72000</v>
       </c>
       <c r="E4" s="10">
@@ -4251,10 +4895,10 @@
       <c r="B5" s="10">
         <v>300</v>
       </c>
-      <c r="C5" s="71">
+      <c r="C5" s="65">
         <v>220</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="63">
         <v>240</v>
       </c>
       <c r="E5" s="10">
@@ -4286,10 +4930,10 @@
       <c r="B6" s="10">
         <v>95</v>
       </c>
-      <c r="C6" s="71">
+      <c r="C6" s="65">
         <v>80</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="63">
         <v>140</v>
       </c>
       <c r="E6" s="10">
@@ -4321,10 +4965,10 @@
       <c r="B7" s="10">
         <v>0.35</v>
       </c>
-      <c r="C7" s="71">
+      <c r="C7" s="65">
         <v>0.37</v>
       </c>
-      <c r="D7" s="69">
+      <c r="D7" s="63">
         <v>0.38</v>
       </c>
       <c r="E7" s="10">
@@ -4356,10 +5000,10 @@
       <c r="B8" s="11">
         <v>75</v>
       </c>
-      <c r="C8" s="72">
+      <c r="C8" s="66">
         <v>95</v>
       </c>
-      <c r="D8" s="70">
+      <c r="D8" s="64">
         <v>90</v>
       </c>
       <c r="E8" s="11">
@@ -4391,10 +5035,10 @@
       <c r="B9" s="11">
         <v>55</v>
       </c>
-      <c r="C9" s="72">
+      <c r="C9" s="75">
         <v>65</v>
       </c>
-      <c r="D9" s="70">
+      <c r="D9" s="64">
         <v>60</v>
       </c>
       <c r="E9" s="11">
@@ -4421,15 +5065,15 @@
     </row>
     <row r="10" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11">
         <v>6560</v>
       </c>
-      <c r="C10" s="72">
+      <c r="C10" s="75">
         <v>3840</v>
       </c>
-      <c r="D10" s="70">
+      <c r="D10" s="64">
         <v>5460</v>
       </c>
       <c r="E10" s="11">
@@ -4456,15 +5100,15 @@
     </row>
     <row r="11" spans="1:11" ht="13.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11">
         <v>19670</v>
       </c>
-      <c r="C11" s="72">
+      <c r="C11" s="66">
         <v>18350</v>
       </c>
-      <c r="D11" s="70">
+      <c r="D11" s="64">
         <v>19960</v>
       </c>
       <c r="E11" s="11">
@@ -4491,15 +5135,15 @@
     </row>
     <row r="12" spans="1:11" ht="13.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="11">
         <v>10</v>
       </c>
-      <c r="C12" s="72">
+      <c r="C12" s="66">
         <v>12</v>
       </c>
-      <c r="D12" s="70">
+      <c r="D12" s="64">
         <v>8</v>
       </c>
       <c r="E12" s="11">
@@ -4526,15 +5170,15 @@
     </row>
     <row r="13" spans="1:11" ht="15.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="11">
         <v>9000</v>
       </c>
-      <c r="C13" s="72">
+      <c r="C13" s="66">
         <v>5500</v>
       </c>
-      <c r="D13" s="70">
+      <c r="D13" s="64">
         <v>6000</v>
       </c>
       <c r="E13" s="11">
@@ -4561,15 +5205,15 @@
     </row>
     <row r="14" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="11">
         <v>2600</v>
       </c>
-      <c r="C14" s="72">
+      <c r="C14" s="75">
         <v>2100</v>
       </c>
-      <c r="D14" s="70">
+      <c r="D14" s="64">
         <v>1700</v>
       </c>
       <c r="E14" s="11">
@@ -4594,17 +5238,17 @@
         <v>110</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15" s="11">
         <v>200</v>
       </c>
-      <c r="C15" s="72">
+      <c r="C15" s="75">
         <v>180</v>
       </c>
-      <c r="D15" s="70">
+      <c r="D15" s="64">
         <v>150</v>
       </c>
       <c r="E15" s="11">
@@ -4631,15 +5275,15 @@
     </row>
     <row r="16" spans="1:11" ht="13.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" s="11">
         <v>200</v>
       </c>
-      <c r="C16" s="72">
+      <c r="C16" s="75">
         <v>650</v>
       </c>
-      <c r="D16" s="70">
+      <c r="D16" s="64">
         <v>220</v>
       </c>
       <c r="E16" s="11">
@@ -4666,15 +5310,15 @@
     </row>
     <row r="17" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="11">
         <v>150</v>
       </c>
-      <c r="C17" s="72">
+      <c r="C17" s="66">
         <v>110</v>
       </c>
-      <c r="D17" s="70">
+      <c r="D17" s="64">
         <v>160</v>
       </c>
       <c r="E17" s="11">
@@ -4701,15 +5345,15 @@
     </row>
     <row r="18" spans="1:11" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18" s="11">
         <v>120</v>
       </c>
-      <c r="C18" s="72">
+      <c r="C18" s="66">
         <v>95</v>
       </c>
-      <c r="D18" s="70">
+      <c r="D18" s="64">
         <v>100</v>
       </c>
       <c r="E18" s="11">
@@ -4736,15 +5380,15 @@
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="11">
         <v>24</v>
       </c>
-      <c r="C19" s="72">
+      <c r="C19" s="75">
         <v>50</v>
       </c>
-      <c r="D19" s="70">
+      <c r="D19" s="64">
         <v>60</v>
       </c>
       <c r="E19" s="11">
@@ -4771,15 +5415,15 @@
     </row>
     <row r="20" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="13">
         <v>15</v>
       </c>
-      <c r="C20" s="71">
+      <c r="C20" s="65">
         <v>12</v>
       </c>
-      <c r="D20" s="69">
+      <c r="D20" s="63">
         <v>18</v>
       </c>
       <c r="E20" s="10">
@@ -4821,7 +5465,7 @@
     </row>
     <row r="22" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="31" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="B22" s="24"/>
       <c r="C22" s="45">
@@ -4839,7 +5483,7 @@
     </row>
     <row r="23" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25">
@@ -4857,7 +5501,7 @@
     </row>
     <row r="24" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="32" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B24" s="25"/>
       <c r="C24" s="25">
@@ -4875,7 +5519,7 @@
     </row>
     <row r="25" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="32" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25">
@@ -4893,7 +5537,7 @@
     </row>
     <row r="26" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="32" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25">
@@ -4963,9 +5607,9 @@
       <c r="J29" s="28"/>
       <c r="K29" s="28"/>
     </row>
-    <row r="30" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="35" t="s">
-        <v>40</v>
+    <row r="30" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="74" t="s">
+        <v>72</v>
       </c>
       <c r="B30" s="29"/>
       <c r="C30" s="29">
@@ -4983,7 +5627,7 @@
     </row>
     <row r="31" spans="1:11" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="35" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="B31" s="29"/>
       <c r="C31" s="29">
@@ -5001,7 +5645,7 @@
     </row>
     <row r="32" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="19">
@@ -5019,7 +5663,7 @@
     </row>
     <row r="33" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -5037,7 +5681,7 @@
         <v>11</v>
       </c>
       <c r="B34" s="22"/>
-      <c r="C34" s="73">
+      <c r="C34" s="67">
         <f>(C22/$C$27*100)</f>
         <v>44.262810252313585</v>
       </c>
@@ -5055,7 +5699,7 @@
         <v>12</v>
       </c>
       <c r="B35" s="23"/>
-      <c r="C35" s="73">
+      <c r="C35" s="67">
         <f>(C23/$C$27*100)</f>
         <v>16.931530827721307</v>
       </c>
@@ -5073,7 +5717,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="23"/>
-      <c r="C36" s="73">
+      <c r="C36" s="67">
         <f>(C24/$C$27*100)</f>
         <v>5.7567204814252451</v>
       </c>
@@ -5091,7 +5735,7 @@
         <v>13</v>
       </c>
       <c r="B37" s="23"/>
-      <c r="C37" s="73">
+      <c r="C37" s="67">
         <f>(C25/$C$27*100)</f>
         <v>7.8205169623688287</v>
       </c>
@@ -5109,7 +5753,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="23"/>
-      <c r="C38" s="73">
+      <c r="C38" s="67">
         <f>(C26/$C$27*100)</f>
         <v>25.228421476171036</v>
       </c>
@@ -5142,7 +5786,7 @@
     </row>
     <row r="40" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A40" s="44" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B40" s="43"/>
       <c r="C40" s="43"/>
@@ -5157,7 +5801,7 @@
     </row>
     <row r="41" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A41" s="44" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B41" s="43"/>
       <c r="C41" s="43"/>
@@ -5172,7 +5816,7 @@
     </row>
     <row r="45" spans="1:12" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="55" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E45" s="56">
         <f>C30</f>
@@ -5187,7 +5831,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D46" s="55" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E46" s="56">
         <f>C31</f>
@@ -5200,7 +5844,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D47" s="55" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E47" s="57">
         <f>C32</f>
@@ -5213,7 +5857,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D48" s="55" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E48" s="58">
         <f>C29</f>
@@ -5227,7 +5871,7 @@
     </row>
     <row r="49" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D49" s="55" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E49" s="55">
         <f>C4</f>
@@ -5300,22 +5944,22 @@
     </row>
     <row r="66" spans="3:8" ht="52.8" x14ac:dyDescent="0.25">
       <c r="C66" s="59" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D66" s="59" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E66" s="59" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F66" s="59" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G66" s="59" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H66" s="59" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="3:8" x14ac:dyDescent="0.25">
@@ -5343,60 +5987,59 @@
         <v>-2258.9386666666669</v>
       </c>
     </row>
-    <row r="68" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="55">
         <v>15000</v>
       </c>
       <c r="D68" s="56">
-        <f t="shared" ref="D67:D81" si="0">$E$45</f>
+        <f t="shared" ref="D68:D80" si="0">$E$45</f>
         <v>3527.9</v>
       </c>
       <c r="E68" s="56">
-        <f t="shared" ref="E68:E81" si="1">$E$46*C68/1000</f>
+        <f t="shared" ref="E68:E80" si="1">$E$46*C68/1000</f>
         <v>7630.25</v>
       </c>
       <c r="F68" s="56">
-        <f t="shared" ref="F68:F81" si="2">D68+E68</f>
+        <f t="shared" ref="F68:F80" si="2">D68+E68</f>
         <v>11158.15</v>
       </c>
       <c r="G68" s="55">
-        <f t="shared" ref="G68:G81" si="3">$E$48*C68/1000</f>
+        <f t="shared" ref="G67:G80" si="3">$E$48*C68/1000</f>
         <v>9533.6919999999991</v>
       </c>
       <c r="H68" s="56">
-        <f t="shared" ref="H68:H81" si="4">G68-F68</f>
+        <f t="shared" ref="H68:H80" si="4">G68-F68</f>
         <v>-1624.4580000000005</v>
       </c>
     </row>
     <row r="69" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C69" s="60">
-        <f>E47</f>
-        <v>27801.477533857083</v>
-      </c>
-      <c r="D69" s="61">
-        <f>$E$45</f>
+      <c r="C69" s="55">
+        <v>20000</v>
+      </c>
+      <c r="D69" s="56">
+        <f t="shared" si="0"/>
         <v>3527.9</v>
       </c>
       <c r="E69" s="56">
         <f t="shared" si="1"/>
-        <v>14142.1482635142</v>
+        <v>10173.666666666666</v>
       </c>
       <c r="F69" s="56">
         <f t="shared" si="2"/>
-        <v>17670.0482635142</v>
+        <v>13701.566666666666</v>
       </c>
       <c r="G69" s="55">
         <f t="shared" si="3"/>
-        <v>17670.048263514203</v>
+        <v>12711.589333333333</v>
       </c>
       <c r="H69" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-989.97733333333235</v>
       </c>
     </row>
     <row r="70" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C70" s="55">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="D70" s="56">
         <f t="shared" si="0"/>
@@ -5404,44 +6047,45 @@
       </c>
       <c r="E70" s="56">
         <f t="shared" si="1"/>
-        <v>10173.666666666666</v>
+        <v>12717.083333333334</v>
       </c>
       <c r="F70" s="56">
         <f t="shared" si="2"/>
-        <v>13701.566666666666</v>
+        <v>16244.983333333334</v>
       </c>
       <c r="G70" s="55">
         <f t="shared" si="3"/>
-        <v>12711.589333333333</v>
+        <v>15889.486666666668</v>
       </c>
       <c r="H70" s="56">
         <f t="shared" si="4"/>
-        <v>-989.97733333333235</v>
+        <v>-355.49666666666599</v>
       </c>
     </row>
     <row r="71" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C71" s="55">
-        <v>25000</v>
-      </c>
-      <c r="D71" s="56">
+      <c r="C71" s="60">
+        <f>E47</f>
+        <v>27801.477533857083</v>
+      </c>
+      <c r="D71" s="61">
         <f t="shared" si="0"/>
         <v>3527.9</v>
       </c>
-      <c r="E71" s="56">
+      <c r="E71" s="61">
         <f t="shared" si="1"/>
-        <v>12717.083333333334</v>
-      </c>
-      <c r="F71" s="56">
+        <v>14142.1482635142</v>
+      </c>
+      <c r="F71" s="61">
         <f t="shared" si="2"/>
-        <v>16244.983333333334</v>
-      </c>
-      <c r="G71" s="55">
+        <v>17670.0482635142</v>
+      </c>
+      <c r="G71" s="62">
         <f t="shared" si="3"/>
-        <v>15889.486666666668</v>
-      </c>
-      <c r="H71" s="56">
+        <v>17670.048263514203</v>
+      </c>
+      <c r="H71" s="61">
         <f t="shared" si="4"/>
-        <v>-355.49666666666599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="3:8" x14ac:dyDescent="0.25">
@@ -5595,26 +6239,26 @@
       </c>
     </row>
     <row r="78" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C78" s="55">
+      <c r="C78" s="62">
         <v>60000</v>
       </c>
-      <c r="D78" s="56">
+      <c r="D78" s="61">
         <f t="shared" si="0"/>
         <v>3527.9</v>
       </c>
-      <c r="E78" s="56">
+      <c r="E78" s="61">
         <f t="shared" si="1"/>
         <v>30521</v>
       </c>
-      <c r="F78" s="56">
+      <c r="F78" s="61">
         <f t="shared" si="2"/>
         <v>34048.9</v>
       </c>
-      <c r="G78" s="55">
+      <c r="G78" s="62">
         <f t="shared" si="3"/>
         <v>38134.767999999996</v>
       </c>
-      <c r="H78" s="56">
+      <c r="H78" s="61">
         <f t="shared" si="4"/>
         <v>4085.8679999999949</v>
       </c>
@@ -5669,30 +6313,30 @@
         <v>5354.8293333333349</v>
       </c>
     </row>
-    <row r="81" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C81" s="62">
-        <f>E49</f>
-        <v>60000</v>
-      </c>
-      <c r="D81" s="61">
-        <f t="shared" si="0"/>
+    <row r="84" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C84" s="76">
+        <f>E47</f>
+        <v>27801.477533857083</v>
+      </c>
+      <c r="D84" s="77">
+        <f>$E$45</f>
         <v>3527.9</v>
       </c>
-      <c r="E81" s="56">
-        <f t="shared" si="1"/>
-        <v>30521</v>
-      </c>
-      <c r="F81" s="56">
-        <f t="shared" si="2"/>
-        <v>34048.9</v>
-      </c>
-      <c r="G81" s="55">
-        <f t="shared" si="3"/>
-        <v>38134.767999999996</v>
-      </c>
-      <c r="H81" s="56">
-        <f t="shared" si="4"/>
-        <v>4085.8679999999949</v>
+      <c r="E84" s="78">
+        <f t="shared" ref="E84" si="5">$E$46*C84/1000</f>
+        <v>14142.1482635142</v>
+      </c>
+      <c r="F84" s="78">
+        <f t="shared" ref="F84" si="6">D84+E84</f>
+        <v>17670.0482635142</v>
+      </c>
+      <c r="G84" s="79">
+        <f t="shared" ref="G84" si="7">$E$48*C84/1000</f>
+        <v>17670.048263514203</v>
+      </c>
+      <c r="H84" s="78">
+        <f t="shared" ref="H84" si="8">G84-F84</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5731,37 +6375,37 @@
     </row>
     <row r="2" spans="1:8" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="37" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="36" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="36" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -5769,7 +6413,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="18" x14ac:dyDescent="0.25">
@@ -5782,7 +6426,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -5795,22 +6439,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="78.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="58.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
@@ -5820,42 +6464,42 @@
     </row>
     <row r="21" spans="1:1" ht="24.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="40" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="40" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="42" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
